--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484791_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484791_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.4768</v>
+        <v>7.2449</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2546</v>
+        <v>4.6259</v>
       </c>
       <c r="F2" t="n">
-        <v>2.2222</v>
+        <v>2.619</v>
       </c>
       <c r="G2" t="n">
         <v>4.2558</v>
@@ -610,13 +610,13 @@
         <v>3.2079</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3451</v>
+        <v>0.4229</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2656</v>
+        <v>0.6369</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6107</v>
+        <v>-0.2139</v>
       </c>
       <c r="V2" t="n">
         <v>1.2452</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>C. GONZALEZ DIAZ</t>
+          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>6.0665</v>
+        <v>5.4386</v>
       </c>
       <c r="E3" t="n">
-        <v>6.3855</v>
+        <v>3.6128</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.319</v>
+        <v>1.8258</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2767</v>
+        <v>2.0196</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.0243</v>
+        <v>-1.5542</v>
       </c>
       <c r="I3" t="n">
-        <v>0.301</v>
+        <v>3.5738</v>
       </c>
       <c r="J3" t="n">
-        <v>1.7519</v>
+        <v>2.6339</v>
       </c>
       <c r="K3" t="n">
-        <v>1.5378</v>
+        <v>-0.0736</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2142</v>
+        <v>2.7075</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.4752</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.562</v>
+        <v>-1.4806</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0868</v>
+        <v>0.8663</v>
       </c>
       <c r="P3" t="n">
-        <v>1.887</v>
+        <v>1.1322</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.1887</v>
+        <v>-1.1322</v>
       </c>
       <c r="R3" t="n">
-        <v>2.0757</v>
+        <v>2.2644</v>
       </c>
       <c r="S3" t="n">
-        <v>2.6576</v>
+        <v>1.0417</v>
       </c>
       <c r="T3" t="n">
-        <v>2.3319</v>
+        <v>0.8658</v>
       </c>
       <c r="U3" t="n">
-        <v>0.3257</v>
+        <v>0.1758</v>
       </c>
       <c r="V3" t="n">
         <v>1.2452</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4904</v>
+        <v>1.2452</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. SALVADOR ESCUDER</t>
+          <t>M. MARISCAL GOMEZ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>4.7961</v>
+        <v>5.406</v>
       </c>
       <c r="E4" t="n">
-        <v>3.2892</v>
+        <v>3.587</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5069</v>
+        <v>1.819</v>
       </c>
       <c r="G4" t="n">
-        <v>5.6236</v>
+        <v>3.458</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3553</v>
+        <v>3.6532</v>
       </c>
       <c r="I4" t="n">
-        <v>5.9789</v>
+        <v>-0.1951</v>
       </c>
       <c r="J4" t="n">
-        <v>5.4796</v>
+        <v>3.5841</v>
       </c>
       <c r="K4" t="n">
-        <v>0.9297</v>
+        <v>4.1258</v>
       </c>
       <c r="L4" t="n">
-        <v>4.5499</v>
+        <v>-0.5417</v>
       </c>
       <c r="M4" t="n">
-        <v>0.144</v>
+        <v>-0.1261</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.285</v>
+        <v>-0.4727</v>
       </c>
       <c r="O4" t="n">
-        <v>1.429</v>
+        <v>0.3466</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.1887</v>
+        <v>1.887</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.0192</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.8305</v>
+        <v>1.887</v>
       </c>
       <c r="S4" t="n">
-        <v>0.9082</v>
+        <v>-0.2598</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8288</v>
+        <v>0.0029</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0794</v>
+        <v>-0.2627</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.547</v>
+        <v>0.3208</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.547</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. MARISCAL GOMEZ</t>
+          <t>D. SALVADOR ESCUDER</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>4.7458</v>
+        <v>5.2816</v>
       </c>
       <c r="E5" t="n">
-        <v>3.1385</v>
+        <v>3.563</v>
       </c>
       <c r="F5" t="n">
-        <v>1.6074</v>
+        <v>1.7186</v>
       </c>
       <c r="G5" t="n">
-        <v>3.458</v>
+        <v>5.6236</v>
       </c>
       <c r="H5" t="n">
-        <v>3.6532</v>
+        <v>-0.3553</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1951</v>
+        <v>5.9789</v>
       </c>
       <c r="J5" t="n">
-        <v>3.5841</v>
+        <v>5.4796</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1258</v>
+        <v>0.9297</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5417</v>
+        <v>4.5499</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1261</v>
+        <v>0.144</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.4727</v>
+        <v>-1.285</v>
       </c>
       <c r="O5" t="n">
-        <v>0.3466</v>
+        <v>1.429</v>
       </c>
       <c r="P5" t="n">
-        <v>1.887</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-3.0192</v>
       </c>
       <c r="R5" t="n">
-        <v>1.887</v>
+        <v>2.8305</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.92</v>
+        <v>1.3937</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4456</v>
+        <v>1.1026</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4744</v>
+        <v>0.291</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3208</v>
+        <v>-1.547</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.3208</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>P. GOMEZ GARCIA-GUTIERREZ</t>
+          <t>C. GONZALEZ DIAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>4.1448</v>
+        <v>4.773</v>
       </c>
       <c r="E6" t="n">
-        <v>2.7157</v>
+        <v>5.1978</v>
       </c>
       <c r="F6" t="n">
-        <v>1.429</v>
+        <v>-0.4248</v>
       </c>
       <c r="G6" t="n">
-        <v>2.0196</v>
+        <v>0.2767</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.5542</v>
+        <v>-0.0243</v>
       </c>
       <c r="I6" t="n">
-        <v>3.5738</v>
+        <v>0.301</v>
       </c>
       <c r="J6" t="n">
-        <v>2.6339</v>
+        <v>1.7519</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0736</v>
+        <v>1.5378</v>
       </c>
       <c r="L6" t="n">
-        <v>2.7075</v>
+        <v>0.2142</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-1.4752</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.4806</v>
+        <v>-1.562</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8663</v>
+        <v>0.0868</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1322</v>
+        <v>1.887</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1322</v>
+        <v>-0.1887</v>
       </c>
       <c r="R6" t="n">
-        <v>2.2644</v>
+        <v>2.0757</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.2522</v>
+        <v>1.3641</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0312</v>
+        <v>1.1442</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.221</v>
+        <v>0.2199</v>
       </c>
       <c r="V6" t="n">
         <v>1.2452</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2452</v>
+        <v>2.4904</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-1.2452</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>3.2182</v>
+        <v>3.4429</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1628</v>
+        <v>0.5727</v>
       </c>
       <c r="F7" t="n">
-        <v>3.0553</v>
+        <v>2.8701</v>
       </c>
       <c r="G7" t="n">
         <v>3.5377</v>
@@ -1000,13 +1000,13 @@
         <v>2.2644</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8883</v>
+        <v>1.113</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3556</v>
+        <v>0.7655</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5326</v>
+        <v>0.3475</v>
       </c>
       <c r="V7" t="n">
         <v>0.3018</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>3.2121</v>
+        <v>2.2617</v>
       </c>
       <c r="E8" t="n">
-        <v>0.9726</v>
+        <v>0.1545</v>
       </c>
       <c r="F8" t="n">
-        <v>2.2395</v>
+        <v>2.1072</v>
       </c>
       <c r="G8" t="n">
         <v>0.1052</v>
@@ -1078,13 +1078,13 @@
         <v>1.887</v>
       </c>
       <c r="S8" t="n">
-        <v>2.9557</v>
+        <v>2.0053</v>
       </c>
       <c r="T8" t="n">
-        <v>2.1279</v>
+        <v>1.3098</v>
       </c>
       <c r="U8" t="n">
-        <v>0.8277</v>
+        <v>0.6955</v>
       </c>
       <c r="V8" t="n">
         <v>-0.6036</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.2802</v>
+        <v>0.5402</v>
       </c>
       <c r="E9" t="n">
-        <v>1.9877</v>
+        <v>1.6181</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7075</v>
+        <v>-1.0779</v>
       </c>
       <c r="G9" t="n">
         <v>0.8453000000000001</v>
@@ -1156,13 +1156,13 @@
         <v>1.887</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8876</v>
+        <v>1.1476</v>
       </c>
       <c r="T9" t="n">
-        <v>1.1503</v>
+        <v>0.7806999999999999</v>
       </c>
       <c r="U9" t="n">
-        <v>0.7372</v>
+        <v>0.3669</v>
       </c>
       <c r="V9" t="n">
         <v>-3.151</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.2128</v>
+        <v>-1.4853</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.9557</v>
+        <v>-2.805</v>
       </c>
       <c r="F10" t="n">
-        <v>1.743</v>
+        <v>1.3197</v>
       </c>
       <c r="G10" t="n">
         <v>1.4213</v>
@@ -1234,13 +1234,13 @@
         <v>2.4531</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4792</v>
+        <v>1.2066</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3527</v>
+        <v>0.798</v>
       </c>
       <c r="U10" t="n">
-        <v>0.8319</v>
+        <v>0.4086</v>
       </c>
       <c r="V10" t="n">
         <v>-1.8488</v>
@@ -1267,19 +1267,19 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>31.7277</v>
+        <v>32.9036</v>
       </c>
       <c r="E11" t="n">
-        <v>18.9509</v>
+        <v>20.1268</v>
       </c>
       <c r="F11" t="n">
-        <v>12.7768</v>
+        <v>12.7767</v>
       </c>
       <c r="G11" t="n">
         <v>21.5432</v>
       </c>
       <c r="H11" t="n">
-        <v>4.875599999999999</v>
+        <v>4.8756</v>
       </c>
       <c r="I11" t="n">
         <v>16.6678</v>
@@ -1291,7 +1291,7 @@
         <v>14.7204</v>
       </c>
       <c r="L11" t="n">
-        <v>9.738300000000002</v>
+        <v>9.738300000000001</v>
       </c>
       <c r="M11" t="n">
         <v>-2.9153</v>
@@ -1303,7 +1303,7 @@
         <v>6.9295</v>
       </c>
       <c r="P11" t="n">
-        <v>4.7175</v>
+        <v>4.717499999999999</v>
       </c>
       <c r="Q11" t="n">
         <v>-16.0395</v>
@@ -1312,19 +1312,19 @@
         <v>20.757</v>
       </c>
       <c r="S11" t="n">
-        <v>8.2593</v>
+        <v>9.4351</v>
       </c>
       <c r="T11" t="n">
-        <v>6.230599999999999</v>
+        <v>7.4064</v>
       </c>
       <c r="U11" t="n">
-        <v>2.0284</v>
+        <v>2.0286</v>
       </c>
       <c r="V11" t="n">
         <v>-2.792199999999999</v>
       </c>
       <c r="W11" t="n">
-        <v>4.301200000000001</v>
+        <v>4.3012</v>
       </c>
       <c r="X11" t="n">
         <v>-7.0934</v>
@@ -1411,7 +1411,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>D. CAMEROS JUAN</t>
+          <t>C. SANCHEZ VIDAL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.1485</v>
+        <v>1.239</v>
       </c>
       <c r="E13" t="n">
-        <v>2.3806</v>
+        <v>1.4899</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.232</v>
+        <v>-0.2509</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2711</v>
+        <v>-1.8287</v>
       </c>
       <c r="H13" t="n">
-        <v>0.5134</v>
+        <v>-1.0714</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.2423</v>
+        <v>-0.7574</v>
       </c>
       <c r="J13" t="n">
-        <v>1.7993</v>
+        <v>0.1323</v>
       </c>
       <c r="K13" t="n">
-        <v>1.717</v>
+        <v>0.1323</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0823</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>-1.5281</v>
+        <v>-1.961</v>
       </c>
       <c r="N13" t="n">
         <v>-1.2036</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.3245</v>
+        <v>-0.7574</v>
       </c>
       <c r="P13" t="n">
-        <v>0.1887</v>
+        <v>0.7548</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.1887</v>
+        <v>-1.887</v>
       </c>
       <c r="R13" t="n">
-        <v>0.3774</v>
+        <v>2.6418</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9905</v>
+        <v>-1.4036</v>
       </c>
       <c r="T13" t="n">
-        <v>0.77</v>
+        <v>-0.4719</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2205</v>
+        <v>-0.9317</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.3018</v>
+        <v>3.7166</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>3.7166</v>
       </c>
       <c r="X13" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>C. SANCHEZ VIDAL</t>
+          <t>D. CAMEROS JUAN</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,73 +1501,73 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.9732</v>
+        <v>0.8154</v>
       </c>
       <c r="E14" t="n">
-        <v>1.1976</v>
+        <v>1.8934</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2244</v>
+        <v>-1.078</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.8287</v>
+        <v>0.2711</v>
       </c>
       <c r="H14" t="n">
-        <v>-1.0714</v>
+        <v>0.5134</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.7574</v>
+        <v>-0.2423</v>
       </c>
       <c r="J14" t="n">
-        <v>0.1323</v>
+        <v>1.7993</v>
       </c>
       <c r="K14" t="n">
-        <v>0.1323</v>
+        <v>1.717</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.0823</v>
       </c>
       <c r="M14" t="n">
-        <v>-1.961</v>
+        <v>-1.5281</v>
       </c>
       <c r="N14" t="n">
         <v>-1.2036</v>
       </c>
       <c r="O14" t="n">
-        <v>-0.7574</v>
+        <v>-0.3245</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7548</v>
+        <v>0.1887</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.887</v>
+        <v>-0.1887</v>
       </c>
       <c r="R14" t="n">
-        <v>2.6418</v>
+        <v>0.3774</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6695</v>
+        <v>0.6574</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.7642</v>
+        <v>0.2829</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9052</v>
+        <v>0.3745</v>
       </c>
       <c r="V14" t="n">
-        <v>3.7166</v>
+        <v>-0.3018</v>
       </c>
       <c r="W14" t="n">
-        <v>3.7166</v>
+        <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. POU CAMPILLO</t>
+          <t>Á. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4917</v>
+        <v>0.317</v>
       </c>
       <c r="E15" t="n">
-        <v>4.8943</v>
+        <v>0.317</v>
       </c>
       <c r="F15" t="n">
-        <v>-4.4026</v>
+        <v>0</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.8625</v>
+        <v>0.317</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2373</v>
+        <v>0.317</v>
       </c>
       <c r="I15" t="n">
-        <v>-3.0998</v>
+        <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>1.631</v>
+        <v>0.317</v>
       </c>
       <c r="K15" t="n">
-        <v>2.8478</v>
+        <v>0.317</v>
       </c>
       <c r="L15" t="n">
-        <v>-1.2169</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.4935</v>
+        <v>0</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.6106</v>
+        <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.8829</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.3209</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.1887</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5096</v>
+        <v>0</v>
       </c>
       <c r="S15" t="n">
-        <v>0.08989999999999999</v>
+        <v>0</v>
       </c>
       <c r="T15" t="n">
-        <v>0.9616</v>
+        <v>0</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.8717</v>
+        <v>0</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9434</v>
+        <v>0</v>
       </c>
       <c r="W15" t="n">
-        <v>2.4904</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Á. PINTO MEDINA</t>
+          <t>A. POU CAMPILLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.317</v>
+        <v>0.0514</v>
       </c>
       <c r="E16" t="n">
-        <v>0.317</v>
+        <v>4.1148</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-4.0634</v>
       </c>
       <c r="G16" t="n">
-        <v>0.317</v>
+        <v>-1.8625</v>
       </c>
       <c r="H16" t="n">
-        <v>0.317</v>
+        <v>1.2373</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-3.0998</v>
       </c>
       <c r="J16" t="n">
-        <v>0.317</v>
+        <v>1.631</v>
       </c>
       <c r="K16" t="n">
-        <v>0.317</v>
+        <v>2.8478</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>-1.2169</v>
       </c>
       <c r="M16" t="n">
-        <v>0</v>
+        <v>-3.4935</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>-1.6106</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-1.8829</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.3209</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-0.1887</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>1.5096</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.3504</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>0.1822</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-0.5325</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.9434</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>2.4904</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.1533</v>
+        <v>-0.2327</v>
       </c>
       <c r="E17" t="n">
         <v>-0.305</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1517</v>
+        <v>0.0723</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3479</v>
@@ -1780,13 +1780,13 @@
         <v>0.5661</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.3715</v>
+        <v>-0.4509</v>
       </c>
       <c r="T17" t="n">
         <v>-0.3527</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0188</v>
+        <v>-0.0982</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.7627</v>
+        <v>-2.4355</v>
       </c>
       <c r="E18" t="n">
-        <v>-2.0382</v>
+        <v>-1.8434</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.7245</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="G18" t="n">
         <v>-1.8486</v>
@@ -1858,13 +1858,13 @@
         <v>0.7548</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7254</v>
+        <v>-0.3983</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2816</v>
+        <v>-0.0867</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.4438</v>
+        <v>-0.3115</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.3302</v>
+        <v>-4.2941</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.9748</v>
+        <v>-1.7799</v>
       </c>
       <c r="F19" t="n">
-        <v>-2.3554</v>
+        <v>-2.5142</v>
       </c>
       <c r="G19" t="n">
         <v>-1.6946</v>
@@ -1936,13 +1936,13 @@
         <v>1.3209</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2016</v>
+        <v>-0.1655</v>
       </c>
       <c r="T19" t="n">
-        <v>0.0152</v>
+        <v>0.2101</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2169</v>
+        <v>-0.3756</v>
       </c>
       <c r="V19" t="n">
         <v>-0.9244</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>V. CARLES TEJEDO</t>
+          <t>A. PINTO MEDINA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-4.4611</v>
+        <v>-4.482</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.3705</v>
+        <v>-2.4582</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0906</v>
+        <v>-2.0238</v>
       </c>
       <c r="G20" t="n">
-        <v>-3.6758</v>
+        <v>-1.7164</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.9659</v>
+        <v>1.1888</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.7099</v>
+        <v>-2.9052</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.1191</v>
+        <v>1.7771</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.4696</v>
+        <v>3.0591</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6496</v>
+        <v>-1.2821</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.5566</v>
+        <v>-3.4935</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.4963</v>
+        <v>-1.8704</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0603</v>
+        <v>-1.6231</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1887</v>
+        <v>-1.6983</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.887</v>
+        <v>-3.9627</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6983</v>
+        <v>2.2644</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5967</v>
+        <v>-1.0672</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.0436</v>
+        <v>-0.2725</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.5531</v>
+        <v>-0.7947</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3208</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. PINTO MEDINA</t>
+          <t>V. CARLES TEJEDO</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.1483</v>
+        <v>-4.8412</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.653</v>
+        <v>-3.5653</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4953</v>
+        <v>-1.2758</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.7164</v>
+        <v>-3.6758</v>
       </c>
       <c r="H21" t="n">
-        <v>1.1888</v>
+        <v>-1.9659</v>
       </c>
       <c r="I21" t="n">
-        <v>-2.9052</v>
+        <v>-1.7099</v>
       </c>
       <c r="J21" t="n">
-        <v>1.7771</v>
+        <v>-1.1191</v>
       </c>
       <c r="K21" t="n">
-        <v>3.0591</v>
+        <v>-0.4696</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2821</v>
+        <v>-0.6496</v>
       </c>
       <c r="M21" t="n">
-        <v>-3.4935</v>
+        <v>-2.5566</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.8704</v>
+        <v>-1.4963</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.6231</v>
+        <v>-1.0603</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.6983</v>
+        <v>-0.1887</v>
       </c>
       <c r="Q21" t="n">
-        <v>-3.9627</v>
+        <v>-1.887</v>
       </c>
       <c r="R21" t="n">
-        <v>2.2644</v>
+        <v>1.6983</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.7336</v>
+        <v>-0.9767</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4674</v>
+        <v>-0.2384</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.2662</v>
+        <v>-0.7383</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.3208</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.2697</v>
+        <v>-4.9425</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.987</v>
+        <v>-2.7921</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2827</v>
+        <v>-2.1504</v>
       </c>
       <c r="G22" t="n">
         <v>-2.4055</v>
@@ -2170,13 +2170,13 @@
         <v>1.887</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.2792</v>
+        <v>-0.952</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.5755</v>
+        <v>-0.3807</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.7036</v>
+        <v>-0.5714</v>
       </c>
       <c r="V22" t="n">
         <v>-1.585</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.6083</v>
+        <v>-5.18</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.3928</v>
+        <v>-3.1979</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.2155</v>
+        <v>-1.9821</v>
       </c>
       <c r="G23" t="n">
         <v>-4.7399</v>
@@ -2248,13 +2248,13 @@
         <v>0.9435</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.6795</v>
+        <v>-0.2513</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2323</v>
+        <v>-0.0374</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4473</v>
+        <v>-0.2139</v>
       </c>
       <c r="V23" t="n">
         <v>0.9434</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.4923</v>
+        <v>-8.011200000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.4127</v>
+        <v>-6.2179</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0796</v>
+        <v>-1.7933</v>
       </c>
       <c r="G24" t="n">
         <v>-3.5791</v>
@@ -2326,13 +2326,13 @@
         <v>2.0757</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.0827</v>
+        <v>-1.6016</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0582</v>
+        <v>-0.8633</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.0246</v>
+        <v>-0.7383</v>
       </c>
       <c r="V24" t="n">
         <v>0</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-31.7277</v>
+        <v>-30.4286</v>
       </c>
       <c r="E25" t="n">
-        <v>-12.7767</v>
+        <v>-12.7768</v>
       </c>
       <c r="F25" t="n">
-        <v>-18.9509</v>
+        <v>-17.6518</v>
       </c>
       <c r="G25" t="n">
         <v>-21.5431</v>
@@ -2377,7 +2377,7 @@
         <v>-16.6676</v>
       </c>
       <c r="J25" t="n">
-        <v>2.915599999999999</v>
+        <v>2.9156</v>
       </c>
       <c r="K25" t="n">
         <v>9.844999999999999</v>
@@ -2392,10 +2392,10 @@
         <v>-14.7205</v>
       </c>
       <c r="O25" t="n">
-        <v>-9.738199999999999</v>
+        <v>-9.738200000000001</v>
       </c>
       <c r="P25" t="n">
-        <v>-4.7175</v>
+        <v>-4.717499999999999</v>
       </c>
       <c r="Q25" t="n">
         <v>-20.757</v>
@@ -2404,13 +2404,13 @@
         <v>16.0395</v>
       </c>
       <c r="S25" t="n">
-        <v>-8.2593</v>
+        <v>-6.960099999999999</v>
       </c>
       <c r="T25" t="n">
-        <v>-2.0287</v>
+        <v>-2.0284</v>
       </c>
       <c r="U25" t="n">
-        <v>-6.230700000000001</v>
+        <v>-4.9316</v>
       </c>
       <c r="V25" t="n">
         <v>2.7922</v>
